--- a/vendbees_app/ventory_sheet.xlsx
+++ b/vendbees_app/ventory_sheet.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor_Master" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machine_Master" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refiller_Master" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor_Purchase" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expiry_tracker" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machine_Refill_Log" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales_Log" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current_Stock" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Product_Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vendor_Master" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Machine_Master" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Refiller_Master" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vendor_Purchase" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="expiry_tracker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Machine_Refill_Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sales_Log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Current_Stock" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Stocks" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Stock_Products" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +36,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,8 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,10 +452,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -562,9 +574,146 @@
           <t>VM001</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Batch_Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Stock_Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Machine_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Created_Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cover_List</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Products</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Units</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Batch_Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Stock_Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cover_Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Product_ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Product_Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Created_Date</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -694,33 +843,13 @@
           <t xml:space="preserve">CHIPS </t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Case count * Quantity </t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>P001</t>
@@ -748,7 +877,6 @@
       <c r="H3" t="n">
         <v>0.05</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>8901491101837</v>
       </c>
@@ -757,19 +885,8 @@
           <t>Quantity tb updated - Vishwathi</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>P002</t>
@@ -797,24 +914,11 @@
       <c r="H4" t="n">
         <v>0.05</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>8901491101844</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>P003</t>
@@ -842,22 +946,8 @@
       <c r="H5" t="n">
         <v>0.05</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>P004</t>
@@ -885,24 +975,11 @@
       <c r="H6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>8901491101820</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>P005</t>
@@ -930,24 +1007,11 @@
       <c r="H7" t="n">
         <v>0.05</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>8901491504782</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>P006</t>
@@ -975,22 +1039,8 @@
       <c r="H8" t="n">
         <v>0.05</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>P007</t>
@@ -1018,24 +1068,11 @@
       <c r="H9" t="n">
         <v>0.05</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>8901491001809</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>P008</t>
@@ -1063,22 +1100,8 @@
       <c r="H10" t="n">
         <v>0.05</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>P009</t>
@@ -1106,24 +1129,11 @@
       <c r="H11" t="n">
         <v>0.05</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>8906090572118</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>P010</t>
@@ -1151,24 +1161,11 @@
       <c r="H12" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>8906090570800</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>P011</t>
@@ -1196,22 +1193,8 @@
       <c r="H13" t="n">
         <v>0.05</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>P012</t>
@@ -1239,22 +1222,8 @@
       <c r="H14" t="n">
         <v>0.05</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>P013</t>
@@ -1282,22 +1251,8 @@
       <c r="H15" t="n">
         <v>0.05</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>P014</t>
@@ -1325,24 +1280,11 @@
       <c r="H16" t="n">
         <v>0.05</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>8906090575263</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>P015</t>
@@ -1370,24 +1312,11 @@
       <c r="H17" t="n">
         <v>0.05</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>8906090572149</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>P016</t>
@@ -1415,24 +1344,11 @@
       <c r="H18" t="n">
         <v>0.05</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>8906090574495</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>P017</t>
@@ -1460,24 +1376,11 @@
       <c r="H19" t="n">
         <v>0.05</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>8906090576253</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>P018</t>
@@ -1505,22 +1408,8 @@
       <c r="H20" t="n">
         <v>0.05</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>P019</t>
@@ -1548,22 +1437,8 @@
       <c r="H21" t="n">
         <v>0.05</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>P020</t>
@@ -1591,22 +1466,8 @@
       <c r="H22" t="n">
         <v>0.05</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>P021</t>
@@ -1634,22 +1495,8 @@
       <c r="H23" t="n">
         <v>0.05</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>P022</t>
@@ -1677,22 +1524,8 @@
       <c r="H24" t="n">
         <v>0.05</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>P023</t>
@@ -1720,24 +1553,11 @@
       <c r="H25" t="n">
         <v>0.05</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>8901491366052</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>P024</t>
@@ -1765,24 +1585,11 @@
       <c r="H26" t="n">
         <v>0.05</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>8901491100533</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>P025</t>
@@ -1810,22 +1617,8 @@
       <c r="H27" t="n">
         <v>0.05</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>P026</t>
@@ -1853,24 +1646,11 @@
       <c r="H28" t="n">
         <v>0.05</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>8901491103442</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>P027</t>
@@ -1898,24 +1678,11 @@
       <c r="H29" t="n">
         <v>0.05</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>8901491103084</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>P028</t>
@@ -1943,24 +1710,11 @@
       <c r="H30" t="n">
         <v>0.05</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>8901491100519</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>P029</t>
@@ -1988,24 +1742,11 @@
       <c r="H31" t="n">
         <v>0.05</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>8906066701115</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>P030</t>
@@ -2033,22 +1774,8 @@
       <c r="H32" t="n">
         <v>0.05</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>P031</t>
@@ -2076,24 +1803,11 @@
       <c r="H33" t="n">
         <v>0.05</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>8901725004903</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>P032</t>
@@ -2121,24 +1835,11 @@
       <c r="H34" t="n">
         <v>0.05</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>8901725111649</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>P033</t>
@@ -2166,24 +1867,11 @@
       <c r="H35" t="n">
         <v>0.05</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>8901725013790</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>P034</t>
@@ -2211,24 +1899,11 @@
       <c r="H36" t="n">
         <v>0.05</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>8901725013721</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>P035</t>
@@ -2256,22 +1931,8 @@
       <c r="H37" t="n">
         <v>0.05</v>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>P036</t>
@@ -2299,24 +1960,11 @@
       <c r="H38" t="n">
         <v>0.05</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>8909081007163</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>P037</t>
@@ -2344,24 +1992,11 @@
       <c r="H39" t="n">
         <v>0.05</v>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>8901725004897</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>P038</t>
@@ -2389,24 +2024,11 @@
       <c r="H40" t="n">
         <v>0.05</v>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>8901725013769</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>P039</t>
@@ -2434,24 +2056,11 @@
       <c r="H41" t="n">
         <v>0.05</v>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>8901725013677</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>P040</t>
@@ -2479,24 +2088,11 @@
       <c r="H42" t="n">
         <v>0.05</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>8901725007553</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>P041</t>
@@ -2524,24 +2120,11 @@
       <c r="H43" t="n">
         <v>0.05</v>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>8901725117788</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>P042</t>
@@ -2569,24 +2152,11 @@
       <c r="H44" t="n">
         <v>0.05</v>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>8901725111649</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>P043</t>
@@ -2614,22 +2184,8 @@
       <c r="H45" t="n">
         <v>0.05</v>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>P044</t>
@@ -2657,24 +2213,11 @@
       <c r="H46" t="n">
         <v>0.05</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>8901491990028</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>P045</t>
@@ -2702,21 +2245,9 @@
       <c r="H47" t="n">
         <v>0.05</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>8901491000192</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2751,22 +2282,8 @@
       <c r="H48" t="n">
         <v>0.05</v>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>P047</t>
@@ -2794,22 +2311,8 @@
       <c r="H49" t="n">
         <v>0.05</v>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>P048</t>
@@ -2837,22 +2340,8 @@
       <c r="H50" t="n">
         <v>0.05</v>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>P049</t>
@@ -2880,24 +2369,11 @@
       <c r="H51" t="n">
         <v>0.05</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>8902979050906</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>P050</t>
@@ -2925,24 +2401,11 @@
       <c r="H52" t="n">
         <v>0.05</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>8902979052399</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>P051</t>
@@ -2970,22 +2433,8 @@
       <c r="H53" t="n">
         <v>0.05</v>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>P052</t>
@@ -3013,22 +2462,8 @@
       <c r="H54" t="n">
         <v>0.05</v>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>P053</t>
@@ -3056,24 +2491,11 @@
       <c r="H55" t="n">
         <v>0.05</v>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>8902979010559</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>P054</t>
@@ -3101,24 +2523,11 @@
       <c r="H56" t="n">
         <v>0.05</v>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>8902979005326</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>P055</t>
@@ -3146,24 +2555,11 @@
       <c r="H57" t="n">
         <v>0.05</v>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>8902979052412</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>P056</t>
@@ -3191,24 +2587,11 @@
       <c r="H58" t="n">
         <v>0.05</v>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>8902979050883</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>P057</t>
@@ -3236,24 +2619,11 @@
       <c r="H59" t="n">
         <v>0.05</v>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>8901071732598</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>P058</t>
@@ -3281,24 +2651,11 @@
       <c r="H60" t="n">
         <v>0.05</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>8901071732468</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>P059</t>
@@ -3326,22 +2683,8 @@
       <c r="H61" t="n">
         <v>0.05</v>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>P060</t>
@@ -3369,22 +2712,8 @@
       <c r="H62" t="n">
         <v>0.05</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>P061</t>
@@ -3412,22 +2741,8 @@
       <c r="H63" t="n">
         <v>0.05</v>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>P062</t>
@@ -3455,22 +2770,8 @@
       <c r="H64" t="n">
         <v>0.05</v>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>P063</t>
@@ -3498,22 +2799,8 @@
       <c r="H65" t="n">
         <v>0.05</v>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>P064</t>
@@ -3541,22 +2828,8 @@
       <c r="H66" t="n">
         <v>0.05</v>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>P065</t>
@@ -3584,22 +2857,8 @@
       <c r="H67" t="n">
         <v>0.05</v>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>P066</t>
@@ -3627,22 +2886,8 @@
       <c r="H68" t="n">
         <v>0.05</v>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>P067</t>
@@ -3670,22 +2915,8 @@
       <c r="H69" t="n">
         <v>0.05</v>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>P068</t>
@@ -3713,22 +2944,8 @@
       <c r="H70" t="n">
         <v>0.05</v>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>P069</t>
@@ -3756,22 +2973,8 @@
       <c r="H71" t="n">
         <v>0.05</v>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>P070</t>
@@ -3799,22 +3002,8 @@
       <c r="H72" t="n">
         <v>0.05</v>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>P071</t>
@@ -3842,22 +3031,8 @@
       <c r="H73" t="n">
         <v>0.4</v>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>P072</t>
@@ -3885,24 +3060,11 @@
       <c r="H74" t="n">
         <v>0.4</v>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
         <v>8901764061257</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>P073</t>
@@ -3930,24 +3092,11 @@
       <c r="H75" t="n">
         <v>0.4</v>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
         <v>8901764011252</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>P074</t>
@@ -3975,22 +3124,8 @@
       <c r="H76" t="n">
         <v>0.4</v>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>P075</t>
@@ -4018,24 +3153,11 @@
       <c r="H77" t="n">
         <v>0.4</v>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
         <v>8902080365043</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>P076</t>
@@ -4063,22 +3185,8 @@
       <c r="H78" t="n">
         <v>0.4</v>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>P077</t>
@@ -4106,22 +3214,8 @@
       <c r="H79" t="n">
         <v>0.4</v>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>P078</t>
@@ -4149,24 +3243,11 @@
       <c r="H80" t="n">
         <v>0.4</v>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
         <v>8902080105045</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>P079</t>
@@ -4194,22 +3275,8 @@
       <c r="H81" t="n">
         <v>0.4</v>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>P080</t>
@@ -4237,24 +3304,11 @@
       <c r="H82" t="n">
         <v>0.4</v>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
         <v>4897036692455</v>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>P081</t>
@@ -4282,24 +3336,11 @@
       <c r="H83" t="n">
         <v>0.4</v>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
         <v>4897036691427</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>P083</t>
@@ -4327,24 +3368,11 @@
       <c r="H84" t="n">
         <v>0.05</v>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
         <v>8901764092800</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>P084</t>
@@ -4372,22 +3400,8 @@
       <c r="H85" t="n">
         <v>0.05</v>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>P085</t>
@@ -4415,22 +3429,8 @@
       <c r="H86" t="n">
         <v>0.05</v>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>P086</t>
@@ -4458,22 +3458,8 @@
       <c r="H87" t="n">
         <v>0.05</v>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>P087</t>
@@ -4501,22 +3487,8 @@
       <c r="H88" t="n">
         <v>0.05</v>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>P088</t>
@@ -4544,22 +3516,8 @@
       <c r="H89" t="n">
         <v>0.05</v>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>P089</t>
@@ -4587,22 +3545,8 @@
       <c r="H90" t="n">
         <v>0.05</v>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>P090</t>
@@ -4630,22 +3574,8 @@
       <c r="H91" t="n">
         <v>0.4</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>P091</t>
@@ -4673,22 +3603,8 @@
       <c r="H92" t="n">
         <v>0.05</v>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>P092</t>
@@ -4716,22 +3632,8 @@
       <c r="H93" t="n">
         <v>0.05</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>P093</t>
@@ -4759,22 +3661,8 @@
       <c r="H94" t="n">
         <v>0.05</v>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>P094</t>
@@ -4802,22 +3690,8 @@
       <c r="H95" t="n">
         <v>0.05</v>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>P095</t>
@@ -4845,22 +3719,8 @@
       <c r="H96" t="n">
         <v>0.05</v>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>P096</t>
@@ -4888,22 +3748,8 @@
       <c r="H97" t="n">
         <v>0.05</v>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>P097</t>
@@ -4931,22 +3777,8 @@
       <c r="H98" t="n">
         <v>0.05</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>P099</t>
@@ -4974,22 +3806,8 @@
       <c r="H99" t="n">
         <v>0.05</v>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>P100</t>
@@ -5017,22 +3835,8 @@
       <c r="H100" t="n">
         <v>0.4</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>P101</t>
@@ -5060,22 +3864,8 @@
       <c r="H101" t="n">
         <v>0.4</v>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>P102</t>
@@ -5103,22 +3893,8 @@
       <c r="H102" t="n">
         <v>0.4</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>P103</t>
@@ -5137,7 +3913,6 @@
       <c r="E103" t="n">
         <v>20</v>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>-</t>
@@ -5146,22 +3921,8 @@
       <c r="H103" t="n">
         <v>0.05</v>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>P104</t>
@@ -5193,22 +3954,8 @@
       <c r="H104" t="n">
         <v>0.05</v>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>P105</t>
@@ -5240,22 +3987,8 @@
       <c r="H105" t="n">
         <v>0.05</v>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>P106</t>
@@ -5287,22 +4020,8 @@
       <c r="H106" t="n">
         <v>0.05</v>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>P107</t>
@@ -5334,22 +4053,8 @@
       <c r="H107" t="n">
         <v>0.05</v>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>P108</t>
@@ -5381,22 +4086,8 @@
       <c r="H108" t="n">
         <v>0.05</v>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>P109</t>
@@ -5428,22 +4119,8 @@
       <c r="H109" t="n">
         <v>0.05</v>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>P110</t>
@@ -5475,22 +4152,8 @@
       <c r="H110" t="n">
         <v>0.05</v>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>P111</t>
@@ -5522,22 +4185,8 @@
       <c r="H111" t="n">
         <v>0.05</v>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>P112</t>
@@ -5569,22 +4218,8 @@
       <c r="H112" t="n">
         <v>0.05</v>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>P113</t>
@@ -5616,22 +4251,8 @@
       <c r="H113" t="n">
         <v>0.05</v>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>P114</t>
@@ -5663,22 +4284,8 @@
       <c r="H114" t="n">
         <v>0.05</v>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>P115</t>
@@ -5710,22 +4317,8 @@
       <c r="H115" t="n">
         <v>0.05</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>P116</t>
@@ -5757,22 +4350,8 @@
       <c r="H116" t="n">
         <v>0.05</v>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>P117</t>
@@ -5804,22 +4383,8 @@
       <c r="H117" t="n">
         <v>0.05</v>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>P118</t>
@@ -5851,19 +4416,6 @@
       <c r="H118" t="n">
         <v>0.05</v>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5902,22 +4454,8 @@
       <c r="H119" t="n">
         <v>0.05</v>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>P120</t>
@@ -5949,22 +4487,8 @@
       <c r="H120" t="n">
         <v>0.05</v>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>P121</t>
@@ -5996,22 +4520,8 @@
       <c r="H121" t="n">
         <v>0.05</v>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>P122</t>
@@ -6043,22 +4553,8 @@
       <c r="H122" t="n">
         <v>0.05</v>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>P123</t>
@@ -6090,22 +4586,8 @@
       <c r="H123" t="n">
         <v>0.05</v>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>P124</t>
@@ -6133,22 +4615,8 @@
       <c r="H124" t="n">
         <v>0.05</v>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>P125</t>
@@ -6176,22 +4644,8 @@
       <c r="H125" t="n">
         <v>0.05</v>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>P126</t>
@@ -6210,7 +4664,6 @@
       <c r="E126" t="n">
         <v>25</v>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>-</t>
@@ -6219,22 +4672,8 @@
       <c r="H126" t="n">
         <v>0.05</v>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>P127</t>
@@ -6266,22 +4705,8 @@
       <c r="H127" t="n">
         <v>0.05</v>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>P128</t>
@@ -6313,19 +4738,6 @@
       <c r="H128" t="n">
         <v>0.05</v>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6364,22 +4776,8 @@
       <c r="H129" t="n">
         <v>0.05</v>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>P130</t>
@@ -6411,22 +4809,8 @@
       <c r="H130" t="n">
         <v>0.05</v>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>P131</t>
@@ -6458,22 +4842,8 @@
       <c r="H131" t="n">
         <v>0.05</v>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>P132</t>
@@ -6505,22 +4875,8 @@
       <c r="H132" t="n">
         <v>0.05</v>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>P133</t>
@@ -6552,22 +4908,8 @@
       <c r="H133" t="n">
         <v>0.05</v>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>P134</t>
@@ -6599,22 +4941,8 @@
       <c r="H134" t="n">
         <v>0.05</v>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>P135</t>
@@ -6646,22 +4974,8 @@
       <c r="H135" t="n">
         <v>0.05</v>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>P136</t>
@@ -6693,22 +5007,8 @@
       <c r="H136" t="n">
         <v>0.05</v>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>P137</t>
@@ -6740,22 +5040,8 @@
       <c r="H137" t="n">
         <v>0.05</v>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>P138</t>
@@ -6787,22 +5073,8 @@
       <c r="H138" t="n">
         <v>0.05</v>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>P139</t>
@@ -6834,22 +5106,8 @@
       <c r="H139" t="n">
         <v>0.05</v>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>P140</t>
@@ -6881,22 +5139,8 @@
       <c r="H140" t="n">
         <v>0.18</v>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>P141</t>
@@ -6928,22 +5172,8 @@
       <c r="H141" t="n">
         <v>0.18</v>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>P142</t>
@@ -6975,19 +5205,6 @@
       <c r="H142" t="n">
         <v>0.18</v>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7051,31 +5268,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                                                                                                                 VENDORS LIST </t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -7123,17 +5322,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -7145,7 +5334,6 @@
           <t>ARA Traders</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>DORITOS</t>
@@ -7169,13 +5357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>DORITOD NACHOS SWEET CHILLI</t>
@@ -7186,29 +5369,15 @@
           <t>,AMINJIKARAI, CHENNAI.600029</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>DORITOS NACHOS CHEESE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>KURKURE</t>
@@ -7219,105 +5388,50 @@
           <t>KURKURE SCHEZWAN CHUTNEY</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>KURKURE PUFFCORN</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>KURKURE CHILLI CHITAKA</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>KURKURE GREEN CHILLI</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>KURKURE NAUGHTY TOMATO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>KURKURE GREEN CHUTNEY</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>KURKURE MUNCH MASALA</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>LAYS</t>
@@ -7328,112 +5442,50 @@
           <t>LAYS CLASSIC SALT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>LAYS MAGIC MASALA</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>LAYS AMERICAN STYLE CREAM ONION</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>LAYS SPANISH TOMATO TANGY</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>LAYS HOT N SWEET CHILLI</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>LAYS WAFER RED CHILLI</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>LAYS SIZZLIN HOT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -7445,7 +5497,6 @@
           <t>Al-AZIZ traders</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>Cool Drinks</t>
@@ -7464,14 +5515,8 @@
       <c r="G24" t="n">
         <v>9884161499</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>COKE TIN ZERO SUGAR</t>
@@ -7482,216 +5527,94 @@
           <t>ALANDUR, CHENNAI - 600016</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>COKE TIN</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>COKE</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>THUMBS UP TIN</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>THUMBS (300ml)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>MAAZA PET BOTTLE</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>MM PULPY ORANGE</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>FANTA</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>MM PULPY ORANGE</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>FANTA</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>7UP TIN</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>SPRITE TIN</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>SPRITE</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Ruby</t>
@@ -7702,52 +5625,22 @@
           <t>RUBY PISTA MILK</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>RUBY BADAM MILK</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>RUBY ROSE MILK</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -7759,7 +5652,6 @@
           <t>A1 Agengy</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Bingo</t>
@@ -7778,7 +5670,6 @@
       <c r="G44" t="n">
         <v>9884161499</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>a1agency2023@gmail.com</t>
@@ -7786,10 +5677,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>BINGO ORGINAL STYLE PINK SALT</t>
@@ -7800,15 +5687,8 @@
           <t>6TH STREET,ADAMBAKKAM,</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>BINGO MM MASALA</t>
@@ -7819,186 +5699,85 @@
           <t>CHENNAI-600088.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>BINGO MAD ANGLES PERI PERI</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>BINGO MASTI CHILLI</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>BINGO TEDHE MEDHE</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>BINGO NACHOS CHILLI</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>BINGO MAD ANGLES TOMATO</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>BINGO MAD ANGLE MASALA ACHARI</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>BINGO CREAM &amp; ONION</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>BINGO TOMATO POTATO CHIPS</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>BINGO CLASSIC SALT</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>DARK FANTASY BOURBON</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>MOM'S MAGIC CASHEW</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -8010,7 +5789,6 @@
           <t>SRI Traders</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t xml:space="preserve">Too Yumm </t>
@@ -8034,13 +5812,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>TOO YUMM KARARE CHILLI ACHARI</t>
@@ -8051,15 +5824,8 @@
           <t>CHATRAPATHI SIVAJI STREET,</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>TOO YUMM CHILI CHATAKA</t>
@@ -8070,15 +5836,8 @@
           <t>SHANMUGA NAGAR, CHITLAPAKKAM</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>TOO YUMM WAFER SPICY CHILLI</t>
@@ -8089,171 +5848,78 @@
           <t>CHENNAI-600064</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>TOO YUMM POTATO SPANISH TOMATO</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>TOO YUMM AMERICAN STYLE CREAM ONION</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>TOO YUMM BHOOT KARARE</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>TOO YUMM KARARE NOODLES MASALA</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>TOO YUMM KARARE TWISTIES</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>TOO YUMM KARARE MUNCH MASALA</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>TOO YUMM KASHMIRI CHILLI</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>TOO YUMM INDIAN MASALA</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>TOO YUMM NAGIN</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>TOO YUMM SOUR CREAM</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
@@ -8265,7 +5931,6 @@
           <t>DivyaLakshmi Traders</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Cream Bell</t>
@@ -8287,13 +5952,8 @@
       <c r="H74" t="n">
         <v>8610495179</v>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>CREAM BELL BADAM MILKSHAKE</t>
@@ -8304,15 +5964,8 @@
           <t>SOUTH JAGANATHAN NAGAR</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>CREAM BELL VANNILA</t>
@@ -8323,96 +5976,43 @@
           <t>VILLIWAKKAM,CHENNAI-600049</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>CREAM BELL COFFEE</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>CREAM BELL CHOCO</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>CREAM BELL BUTTER SCOTCH</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>PEPSI TIN</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>PEPSI ZERO SUGAR TIN</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -8424,7 +6024,6 @@
           <t>Sithi Vinayagar Traders</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>Tropicana</t>
@@ -8446,13 +6045,8 @@
       <c r="H83" t="n">
         <v>8610495179</v>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>TROPICANA APPLE</t>
@@ -8463,15 +6057,8 @@
           <t xml:space="preserve">SOUTH JAGANNATH NAGAR, VILLIVAKAM </t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>TROPICANA SLICE</t>
@@ -8482,148 +6069,59 @@
           <t>CHENNAI-49</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>TROPICANA ORANGE</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>TROPICANA POMEGRANATE</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>TROPICANA GUVA</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>TROPICANA LITCHI DELIGHT</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>LIPTON ICE TEA</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t xml:space="preserve">Black Pepsi </t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Mountain dew</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
@@ -8635,7 +6133,6 @@
           <t>Amma Agency</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>Hershey's</t>
@@ -8654,14 +6151,8 @@
       <c r="G96" t="n">
         <v>9444387479</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>HERSHEY’S VANILLA MILKSHAKE</t>
@@ -8672,15 +6163,8 @@
           <t>MOHANRAM NAGAR</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>HERSHEY'S COOKIES AND CREAM</t>
@@ -8691,74 +6175,36 @@
           <t>MOGAPAIR EAST, CHENNAI-37</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>HERSHEY'S ALMOND FLAVOR</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>HERSHEY'S CHOCOLATE FLAVOR</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>HERSHEY'S COFFEE MOCHA FLAVOR</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>HERSHEY'S STRAWBERRY FLAVOR</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>Softi</t>
@@ -8769,15 +6215,8 @@
           <t>SOFIT SOYA CHOCOLATE FLAVOR</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>CAVINS</t>
@@ -8788,127 +6227,57 @@
           <t>CAVINS BUTTERSCOTCH</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>CAVINS CHOCOLATE</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>CAVINS PREMIUM MALT MILKSHAKE</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>CAVINS ORANGE</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>CAVINS BELGIAN CHOCOLATE</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>CAVINS COLD COFFEE</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>CAVINS STRAWBERRY</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>CAVINS VANILLA</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -8920,7 +6289,6 @@
           <t>Shree Markting</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>Ocean Drink</t>
@@ -8944,13 +6312,8 @@
       <c r="H113" t="n">
         <v>9841092481</v>
       </c>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>OCEAN DRINK GREEN APPLE</t>
@@ -8961,54 +6324,27 @@
           <t>VILLIVAKAM CHENNAI-49</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>OCEAN DRINK PEACH &amp; PASSION</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>OCEAN DRINK MANGO &amp; PASSION</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>OCEAN PINK GUVA</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9277,15 +6613,9 @@
           <t>ARA01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>33FQBPD79901ZZ</t>
@@ -9296,15 +6626,11 @@
           <t>IMPS</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9317,15 +6643,9 @@
           <t>AIAZ02</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>50</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>33AYBPA5104A1ZL</t>
@@ -9336,9 +6656,6 @@
           <t>RTGS</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>no</t>
@@ -9361,15 +6678,9 @@
           <t>A103</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>200</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>33FNQPS7197G1Z4</t>
@@ -9380,10 +6691,6 @@
           <t>NEFT</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>GST@0%</t>
@@ -9401,15 +6708,9 @@
           <t>SRI04</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>150</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>33APNPG3932K1ZS</t>
@@ -9420,10 +6721,6 @@
           <t>GPAY</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>GST@0.25%</t>
@@ -9441,15 +6738,9 @@
           <t>D05</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>50</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>33AAWFD5467C1Z9</t>
@@ -9460,10 +6751,6 @@
           <t>PAYTM</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>GST@3%</t>
@@ -9481,13 +6768,6 @@
           <t>AA07</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>33A1GPR5884F1ZY</t>
@@ -9498,10 +6778,6 @@
           <t>CASH</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>GST@5%</t>
@@ -9519,23 +6795,11 @@
           <t>SM08</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>33AL0PS4454M1ZG</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>GST@12%</t>
@@ -9543,21 +6807,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>GST@18%</t>
@@ -9565,21 +6814,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>GST@28%</t>
@@ -9587,25 +6821,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">B and M column to be mapped along with GST % value </t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>GST@40%</t>
@@ -9745,7 +6965,6 @@
           <t>P001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>20</v>
       </c>
@@ -9771,7 +6990,6 @@
           <t>P004</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>30</v>
       </c>
@@ -9797,7 +7015,6 @@
           <t>P007</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>25</v>
       </c>
@@ -9823,7 +7040,6 @@
           <t>P010</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>10</v>
       </c>
@@ -9849,7 +7065,6 @@
           <t>P007</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>50</v>
       </c>
@@ -9875,7 +7090,6 @@
           <t>P010</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>50</v>
       </c>
@@ -9937,7 +7151,6 @@
           <t>VM001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>10</v>
       </c>
@@ -10026,49 +7239,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">Alert notification - low ,moderate </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
